--- a/Data/Rules/Evangers Rules Matrix.xlsx
+++ b/Data/Rules/Evangers Rules Matrix.xlsx
@@ -1625,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J7">
         <v>12</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J8">
         <v>12</v>
@@ -1869,7 +1869,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J9">
         <v>12</v>
@@ -1991,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J10">
         <v>12</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J11">
         <v>12</v>
@@ -2232,13 +2232,13 @@
         <v>12</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -2354,13 +2354,13 @@
         <v>12</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -2476,13 +2476,13 @@
         <v>12</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -2598,13 +2598,13 @@
         <v>12</v>
       </c>
       <c r="H15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2720,13 +2720,13 @@
         <v>24</v>
       </c>
       <c r="H16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -2842,13 +2842,13 @@
         <v>12</v>
       </c>
       <c r="H17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -2860,13 +2860,13 @@
         <v>12</v>
       </c>
       <c r="N17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
@@ -2964,13 +2964,13 @@
         <v>24</v>
       </c>
       <c r="H18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
@@ -3086,13 +3086,13 @@
         <v>12</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -3104,13 +3104,13 @@
         <v>12</v>
       </c>
       <c r="N19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="b">
         <v>1</v>
@@ -3208,13 +3208,13 @@
         <v>24</v>
       </c>
       <c r="H20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3330,13 +3330,13 @@
         <v>24</v>
       </c>
       <c r="H21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -3452,13 +3452,13 @@
         <v>24</v>
       </c>
       <c r="H22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
@@ -3574,13 +3574,13 @@
         <v>24</v>
       </c>
       <c r="H23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -3696,13 +3696,13 @@
         <v>24</v>
       </c>
       <c r="H24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -4306,13 +4306,13 @@
         <v>24</v>
       </c>
       <c r="H29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -4428,13 +4428,13 @@
         <v>24</v>
       </c>
       <c r="H30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -4455,13 +4455,13 @@
         <v>24</v>
       </c>
       <c r="Q30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T30" t="b">
         <v>0</v>
@@ -4916,13 +4916,13 @@
         <v>12</v>
       </c>
       <c r="H34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J34">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -5038,13 +5038,13 @@
         <v>12</v>
       </c>
       <c r="H35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -5160,13 +5160,13 @@
         <v>12</v>
       </c>
       <c r="H36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -5190,7 +5190,7 @@
         <v>0</v>
       </c>
       <c r="R36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S36">
         <v>12</v>
@@ -5208,7 +5208,7 @@
         <v>0</v>
       </c>
       <c r="X36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y36">
         <v>12</v>
@@ -5226,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="AD36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE36">
         <v>12</v>
@@ -5282,13 +5282,13 @@
         <v>12</v>
       </c>
       <c r="H37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J37">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
@@ -5312,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="R37">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S37">
         <v>12</v>
@@ -5330,7 +5330,7 @@
         <v>0</v>
       </c>
       <c r="X37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y37">
         <v>12</v>
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="AD37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE37">
         <v>12</v>
@@ -5404,13 +5404,13 @@
         <v>12</v>
       </c>
       <c r="H38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -5452,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="X38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y38">
         <v>12</v>
@@ -5526,13 +5526,13 @@
         <v>12</v>
       </c>
       <c r="H39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -5574,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="X39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y39">
         <v>12</v>
@@ -5592,7 +5592,7 @@
         <v>0</v>
       </c>
       <c r="AD39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE39">
         <v>12</v>
@@ -5648,13 +5648,13 @@
         <v>12</v>
       </c>
       <c r="H40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J40">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>12</v>
       </c>
       <c r="H41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -5818,7 +5818,7 @@
         <v>0</v>
       </c>
       <c r="X41">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y41">
         <v>12</v>
@@ -5836,7 +5836,7 @@
         <v>0</v>
       </c>
       <c r="AD41">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE41">
         <v>12</v>
@@ -5892,13 +5892,13 @@
         <v>12</v>
       </c>
       <c r="H42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J42">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -5940,7 +5940,7 @@
         <v>0</v>
       </c>
       <c r="X42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y42">
         <v>12</v>
@@ -6014,13 +6014,13 @@
         <v>12</v>
       </c>
       <c r="H43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -6062,7 +6062,7 @@
         <v>0</v>
       </c>
       <c r="X43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y43">
         <v>12</v>
@@ -6136,13 +6136,13 @@
         <v>12</v>
       </c>
       <c r="H44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J44">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="X44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y44">
         <v>12</v>
@@ -6324,10 +6324,10 @@
         <v>0</v>
       </c>
       <c r="AD45">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AE45">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AF45" t="b">
         <v>0</v>
@@ -6690,10 +6690,10 @@
         <v>0</v>
       </c>
       <c r="AD48">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AE48">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AF48" t="b">
         <v>0</v>
@@ -6746,13 +6746,13 @@
         <v>24</v>
       </c>
       <c r="H49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -6779,7 +6779,7 @@
         <v>2</v>
       </c>
       <c r="S49">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="T49" t="b">
         <v>0</v>
@@ -6868,13 +6868,13 @@
         <v>12</v>
       </c>
       <c r="H50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J50">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -6934,10 +6934,10 @@
         <v>0</v>
       </c>
       <c r="AD50">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AE50">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AF50" t="b">
         <v>0</v>
@@ -6990,13 +6990,13 @@
         <v>12</v>
       </c>
       <c r="H51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J51">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -7112,13 +7112,13 @@
         <v>12</v>
       </c>
       <c r="H52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J52">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K52" t="b">
         <v>0</v>
@@ -7234,13 +7234,13 @@
         <v>12</v>
       </c>
       <c r="H53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J53">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K53" t="b">
         <v>0</v>
@@ -7356,13 +7356,13 @@
         <v>12</v>
       </c>
       <c r="H54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J54">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K54" t="b">
         <v>0</v>
@@ -7478,13 +7478,13 @@
         <v>12</v>
       </c>
       <c r="H55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J55">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K55" t="b">
         <v>0</v>
@@ -7600,13 +7600,13 @@
         <v>12</v>
       </c>
       <c r="H56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J56">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K56" t="b">
         <v>0</v>
@@ -7722,13 +7722,13 @@
         <v>12</v>
       </c>
       <c r="H57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J57">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K57" t="b">
         <v>0</v>
@@ -7844,13 +7844,13 @@
         <v>12</v>
       </c>
       <c r="H58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J58">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K58" t="b">
         <v>0</v>
@@ -7874,7 +7874,7 @@
         <v>0</v>
       </c>
       <c r="R58">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S58">
         <v>24</v>
@@ -7966,13 +7966,13 @@
         <v>12</v>
       </c>
       <c r="H59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J59">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K59" t="b">
         <v>0</v>
@@ -8088,13 +8088,13 @@
         <v>12</v>
       </c>
       <c r="H60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J60">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K60" t="b">
         <v>0</v>
@@ -8210,13 +8210,13 @@
         <v>12</v>
       </c>
       <c r="H61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J61">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K61" t="b">
         <v>0</v>
@@ -8332,13 +8332,13 @@
         <v>12</v>
       </c>
       <c r="H62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J62">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K62" t="b">
         <v>0</v>
@@ -8454,13 +8454,13 @@
         <v>12</v>
       </c>
       <c r="H63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J63">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K63" t="b">
         <v>0</v>
@@ -8576,13 +8576,13 @@
         <v>12</v>
       </c>
       <c r="H64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J64">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K64" t="b">
         <v>0</v>
@@ -8698,13 +8698,13 @@
         <v>12</v>
       </c>
       <c r="H65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J65">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K65" t="b">
         <v>0</v>
@@ -8820,13 +8820,13 @@
         <v>12</v>
       </c>
       <c r="H66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J66">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K66" t="b">
         <v>0</v>
@@ -8942,13 +8942,13 @@
         <v>12</v>
       </c>
       <c r="H67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J67">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K67" t="b">
         <v>0</v>

--- a/Data/Rules/Evangers Rules Matrix.xlsx
+++ b/Data/Rules/Evangers Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="174">
   <si>
     <t>SKU</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>HQ_Max</t>
+  </si>
+  <si>
+    <t>Total Max</t>
   </si>
   <si>
     <t>12899</t>
@@ -864,10 +867,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN67"/>
+  <dimension ref="A1:AO67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -988,16 +991,19 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D2">
         <v>24</v>
@@ -1033,10 +1039,10 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
@@ -1110,16 +1116,19 @@
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>228</v>
+      </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D3">
         <v>24</v>
@@ -1155,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
@@ -1232,16 +1241,19 @@
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>228</v>
+      </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:41">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D4">
         <v>24</v>
@@ -1277,10 +1289,10 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P4">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
@@ -1354,16 +1366,19 @@
       <c r="AN4">
         <v>0</v>
       </c>
+      <c r="AO4">
+        <v>228</v>
+      </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:41">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D5">
         <v>24</v>
@@ -1399,10 +1414,10 @@
         <v>0</v>
       </c>
       <c r="O5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P5">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -1476,16 +1491,19 @@
       <c r="AN5">
         <v>0</v>
       </c>
+      <c r="AO5">
+        <v>228</v>
+      </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:41">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D6">
         <v>24</v>
@@ -1521,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="O6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="P6">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
@@ -1598,16 +1616,19 @@
       <c r="AN6">
         <v>0</v>
       </c>
+      <c r="AO6">
+        <v>228</v>
+      </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:41">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D7">
         <v>12</v>
@@ -1720,16 +1741,19 @@
       <c r="AN7">
         <v>0</v>
       </c>
+      <c r="AO7">
+        <v>120</v>
+      </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:41">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D8">
         <v>12</v>
@@ -1842,16 +1866,19 @@
       <c r="AN8">
         <v>0</v>
       </c>
+      <c r="AO8">
+        <v>120</v>
+      </c>
     </row>
-    <row r="9" spans="1:40">
+    <row r="9" spans="1:41">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D9">
         <v>12</v>
@@ -1964,16 +1991,19 @@
       <c r="AN9">
         <v>0</v>
       </c>
+      <c r="AO9">
+        <v>120</v>
+      </c>
     </row>
-    <row r="10" spans="1:40">
+    <row r="10" spans="1:41">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D10">
         <v>12</v>
@@ -2086,16 +2116,19 @@
       <c r="AN10">
         <v>0</v>
       </c>
+      <c r="AO10">
+        <v>120</v>
+      </c>
     </row>
-    <row r="11" spans="1:40">
+    <row r="11" spans="1:41">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D11">
         <v>12</v>
@@ -2208,16 +2241,19 @@
       <c r="AN11">
         <v>0</v>
       </c>
+      <c r="AO11">
+        <v>120</v>
+      </c>
     </row>
-    <row r="12" spans="1:40">
+    <row r="12" spans="1:41">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D12">
         <v>12</v>
@@ -2330,16 +2366,19 @@
       <c r="AN12">
         <v>0</v>
       </c>
+      <c r="AO12">
+        <v>108</v>
+      </c>
     </row>
-    <row r="13" spans="1:40">
+    <row r="13" spans="1:41">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -2452,16 +2491,19 @@
       <c r="AN13">
         <v>0</v>
       </c>
+      <c r="AO13">
+        <v>96</v>
+      </c>
     </row>
-    <row r="14" spans="1:40">
+    <row r="14" spans="1:41">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D14">
         <v>12</v>
@@ -2574,16 +2616,19 @@
       <c r="AN14">
         <v>0</v>
       </c>
+      <c r="AO14">
+        <v>96</v>
+      </c>
     </row>
-    <row r="15" spans="1:40">
+    <row r="15" spans="1:41">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D15">
         <v>12</v>
@@ -2696,16 +2741,19 @@
       <c r="AN15">
         <v>0</v>
       </c>
+      <c r="AO15">
+        <v>96</v>
+      </c>
     </row>
-    <row r="16" spans="1:40">
+    <row r="16" spans="1:41">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D16">
         <v>24</v>
@@ -2741,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="O16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P16">
         <v>24</v>
@@ -2818,16 +2866,19 @@
       <c r="AN16">
         <v>0</v>
       </c>
+      <c r="AO16">
+        <v>192</v>
+      </c>
     </row>
-    <row r="17" spans="1:40">
+    <row r="17" spans="1:41">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D17">
         <v>12</v>
@@ -2940,16 +2991,19 @@
       <c r="AN17">
         <v>0</v>
       </c>
+      <c r="AO17">
+        <v>84</v>
+      </c>
     </row>
-    <row r="18" spans="1:40">
+    <row r="18" spans="1:41">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D18">
         <v>24</v>
@@ -2985,10 +3039,10 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P18">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="b">
         <v>1</v>
@@ -3062,16 +3116,19 @@
       <c r="AN18">
         <v>0</v>
       </c>
+      <c r="AO18">
+        <v>180</v>
+      </c>
     </row>
-    <row r="19" spans="1:40">
+    <row r="19" spans="1:41">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D19">
         <v>12</v>
@@ -3184,16 +3241,19 @@
       <c r="AN19">
         <v>0</v>
       </c>
+      <c r="AO19">
+        <v>84</v>
+      </c>
     </row>
-    <row r="20" spans="1:40">
+    <row r="20" spans="1:41">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D20">
         <v>24</v>
@@ -3229,10 +3289,10 @@
         <v>0</v>
       </c>
       <c r="O20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P20">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q20" t="b">
         <v>1</v>
@@ -3306,16 +3366,19 @@
       <c r="AN20">
         <v>0</v>
       </c>
+      <c r="AO20">
+        <v>180</v>
+      </c>
     </row>
-    <row r="21" spans="1:40">
+    <row r="21" spans="1:41">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D21">
         <v>24</v>
@@ -3351,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="O21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P21">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
@@ -3428,16 +3491,19 @@
       <c r="AN21">
         <v>0</v>
       </c>
+      <c r="AO21">
+        <v>204</v>
+      </c>
     </row>
-    <row r="22" spans="1:40">
+    <row r="22" spans="1:41">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D22">
         <v>24</v>
@@ -3473,10 +3539,10 @@
         <v>0</v>
       </c>
       <c r="O22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P22">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q22" t="b">
         <v>0</v>
@@ -3550,16 +3616,19 @@
       <c r="AN22">
         <v>0</v>
       </c>
+      <c r="AO22">
+        <v>204</v>
+      </c>
     </row>
-    <row r="23" spans="1:40">
+    <row r="23" spans="1:41">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C23" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D23">
         <v>24</v>
@@ -3595,10 +3664,10 @@
         <v>0</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P23">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
@@ -3672,16 +3741,19 @@
       <c r="AN23">
         <v>0</v>
       </c>
+      <c r="AO23">
+        <v>204</v>
+      </c>
     </row>
-    <row r="24" spans="1:40">
+    <row r="24" spans="1:41">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D24">
         <v>24</v>
@@ -3708,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>24</v>
@@ -3794,16 +3866,19 @@
       <c r="AN24">
         <v>0</v>
       </c>
+      <c r="AO24">
+        <v>216</v>
+      </c>
     </row>
-    <row r="25" spans="1:40">
+    <row r="25" spans="1:41">
       <c r="A25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C25" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -3839,10 +3914,10 @@
         <v>0</v>
       </c>
       <c r="O25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P25">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q25" t="b">
         <v>0</v>
@@ -3916,16 +3991,19 @@
       <c r="AN25">
         <v>0</v>
       </c>
+      <c r="AO25">
+        <v>228</v>
+      </c>
     </row>
-    <row r="26" spans="1:40">
+    <row r="26" spans="1:41">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C26" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D26">
         <v>24</v>
@@ -3961,10 +4039,10 @@
         <v>0</v>
       </c>
       <c r="O26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P26">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q26" t="b">
         <v>0</v>
@@ -4038,16 +4116,19 @@
       <c r="AN26">
         <v>0</v>
       </c>
+      <c r="AO26">
+        <v>228</v>
+      </c>
     </row>
-    <row r="27" spans="1:40">
+    <row r="27" spans="1:41">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C27" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D27">
         <v>24</v>
@@ -4083,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="O27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P27">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q27" t="b">
         <v>0</v>
@@ -4160,16 +4241,19 @@
       <c r="AN27">
         <v>0</v>
       </c>
+      <c r="AO27">
+        <v>228</v>
+      </c>
     </row>
-    <row r="28" spans="1:40">
+    <row r="28" spans="1:41">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D28">
         <v>24</v>
@@ -4196,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>24</v>
@@ -4205,10 +4289,10 @@
         <v>0</v>
       </c>
       <c r="O28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P28">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q28" t="b">
         <v>0</v>
@@ -4282,16 +4366,19 @@
       <c r="AN28">
         <v>0</v>
       </c>
+      <c r="AO28">
+        <v>228</v>
+      </c>
     </row>
-    <row r="29" spans="1:40">
+    <row r="29" spans="1:41">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C29" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D29">
         <v>24</v>
@@ -4327,10 +4414,10 @@
         <v>0</v>
       </c>
       <c r="O29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P29">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q29" t="b">
         <v>0</v>
@@ -4404,16 +4491,19 @@
       <c r="AN29">
         <v>0</v>
       </c>
+      <c r="AO29">
+        <v>204</v>
+      </c>
     </row>
-    <row r="30" spans="1:40">
+    <row r="30" spans="1:41">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C30" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D30">
         <v>24</v>
@@ -4526,16 +4616,19 @@
       <c r="AN30">
         <v>0</v>
       </c>
+      <c r="AO30">
+        <v>216</v>
+      </c>
     </row>
-    <row r="31" spans="1:40">
+    <row r="31" spans="1:41">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -4648,16 +4741,19 @@
       <c r="AN31">
         <v>0</v>
       </c>
+      <c r="AO31">
+        <v>15</v>
+      </c>
     </row>
-    <row r="32" spans="1:40">
+    <row r="32" spans="1:41">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C32" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -4770,16 +4866,19 @@
       <c r="AN32">
         <v>0</v>
       </c>
+      <c r="AO32">
+        <v>14</v>
+      </c>
     </row>
-    <row r="33" spans="1:40">
+    <row r="33" spans="1:41">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -4892,16 +4991,19 @@
       <c r="AN33">
         <v>0</v>
       </c>
+      <c r="AO33">
+        <v>18</v>
+      </c>
     </row>
-    <row r="34" spans="1:40">
+    <row r="34" spans="1:41">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C34" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D34">
         <v>12</v>
@@ -5014,16 +5116,19 @@
       <c r="AN34">
         <v>0</v>
       </c>
+      <c r="AO34">
+        <v>108</v>
+      </c>
     </row>
-    <row r="35" spans="1:40">
+    <row r="35" spans="1:41">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C35" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D35">
         <v>12</v>
@@ -5136,16 +5241,19 @@
       <c r="AN35">
         <v>0</v>
       </c>
+      <c r="AO35">
+        <v>108</v>
+      </c>
     </row>
-    <row r="36" spans="1:40">
+    <row r="36" spans="1:41">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C36" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D36">
         <v>12</v>
@@ -5258,16 +5366,19 @@
       <c r="AN36">
         <v>0</v>
       </c>
+      <c r="AO36">
+        <v>108</v>
+      </c>
     </row>
-    <row r="37" spans="1:40">
+    <row r="37" spans="1:41">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C37" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D37">
         <v>12</v>
@@ -5380,16 +5491,19 @@
       <c r="AN37">
         <v>0</v>
       </c>
+      <c r="AO37">
+        <v>108</v>
+      </c>
     </row>
-    <row r="38" spans="1:40">
+    <row r="38" spans="1:41">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D38">
         <v>12</v>
@@ -5502,16 +5616,19 @@
       <c r="AN38">
         <v>0</v>
       </c>
+      <c r="AO38">
+        <v>144</v>
+      </c>
     </row>
-    <row r="39" spans="1:40">
+    <row r="39" spans="1:41">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B39" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C39" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D39">
         <v>12</v>
@@ -5624,16 +5741,19 @@
       <c r="AN39">
         <v>0</v>
       </c>
+      <c r="AO39">
+        <v>108</v>
+      </c>
     </row>
-    <row r="40" spans="1:40">
+    <row r="40" spans="1:41">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C40" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D40">
         <v>12</v>
@@ -5746,16 +5866,19 @@
       <c r="AN40">
         <v>0</v>
       </c>
+      <c r="AO40">
+        <v>180</v>
+      </c>
     </row>
-    <row r="41" spans="1:40">
+    <row r="41" spans="1:41">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C41" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D41">
         <v>12</v>
@@ -5868,16 +5991,19 @@
       <c r="AN41">
         <v>0</v>
       </c>
+      <c r="AO41">
+        <v>108</v>
+      </c>
     </row>
-    <row r="42" spans="1:40">
+    <row r="42" spans="1:41">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C42" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D42">
         <v>12</v>
@@ -5990,16 +6116,19 @@
       <c r="AN42">
         <v>0</v>
       </c>
+      <c r="AO42">
+        <v>144</v>
+      </c>
     </row>
-    <row r="43" spans="1:40">
+    <row r="43" spans="1:41">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B43" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C43" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D43">
         <v>12</v>
@@ -6112,16 +6241,19 @@
       <c r="AN43">
         <v>0</v>
       </c>
+      <c r="AO43">
+        <v>108</v>
+      </c>
     </row>
-    <row r="44" spans="1:40">
+    <row r="44" spans="1:41">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B44" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C44" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D44">
         <v>12</v>
@@ -6234,16 +6366,19 @@
       <c r="AN44">
         <v>0</v>
       </c>
+      <c r="AO44">
+        <v>108</v>
+      </c>
     </row>
-    <row r="45" spans="1:40">
+    <row r="45" spans="1:41">
       <c r="A45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C45" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D45">
         <v>12</v>
@@ -6356,16 +6491,19 @@
       <c r="AN45">
         <v>0</v>
       </c>
+      <c r="AO45">
+        <v>132</v>
+      </c>
     </row>
-    <row r="46" spans="1:40">
+    <row r="46" spans="1:41">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B46" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C46" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D46">
         <v>12</v>
@@ -6478,16 +6616,19 @@
       <c r="AN46">
         <v>0</v>
       </c>
+      <c r="AO46">
+        <v>120</v>
+      </c>
     </row>
-    <row r="47" spans="1:40">
+    <row r="47" spans="1:41">
       <c r="A47" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C47" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D47">
         <v>12</v>
@@ -6600,16 +6741,19 @@
       <c r="AN47">
         <v>0</v>
       </c>
+      <c r="AO47">
+        <v>120</v>
+      </c>
     </row>
-    <row r="48" spans="1:40">
+    <row r="48" spans="1:41">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B48" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C48" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D48">
         <v>12</v>
@@ -6722,16 +6866,19 @@
       <c r="AN48">
         <v>0</v>
       </c>
+      <c r="AO48">
+        <v>132</v>
+      </c>
     </row>
-    <row r="49" spans="1:40">
+    <row r="49" spans="1:41">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B49" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C49" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D49">
         <v>24</v>
@@ -6844,16 +6991,19 @@
       <c r="AN49">
         <v>0</v>
       </c>
+      <c r="AO49">
+        <v>192</v>
+      </c>
     </row>
-    <row r="50" spans="1:40">
+    <row r="50" spans="1:41">
       <c r="A50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C50" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D50">
         <v>12</v>
@@ -6966,16 +7116,19 @@
       <c r="AN50">
         <v>0</v>
       </c>
+      <c r="AO50">
+        <v>120</v>
+      </c>
     </row>
-    <row r="51" spans="1:40">
+    <row r="51" spans="1:41">
       <c r="A51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B51" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C51" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D51">
         <v>12</v>
@@ -7011,7 +7164,7 @@
         <v>0</v>
       </c>
       <c r="O51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P51">
         <v>12</v>
@@ -7088,16 +7241,19 @@
       <c r="AN51">
         <v>0</v>
       </c>
+      <c r="AO51">
+        <v>108</v>
+      </c>
     </row>
-    <row r="52" spans="1:40">
+    <row r="52" spans="1:41">
       <c r="A52" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B52" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C52" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D52">
         <v>12</v>
@@ -7210,16 +7366,19 @@
       <c r="AN52">
         <v>0</v>
       </c>
+      <c r="AO52">
+        <v>96</v>
+      </c>
     </row>
-    <row r="53" spans="1:40">
+    <row r="53" spans="1:41">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B53" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D53">
         <v>12</v>
@@ -7332,16 +7491,19 @@
       <c r="AN53">
         <v>0</v>
       </c>
+      <c r="AO53">
+        <v>108</v>
+      </c>
     </row>
-    <row r="54" spans="1:40">
+    <row r="54" spans="1:41">
       <c r="A54" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B54" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C54" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D54">
         <v>12</v>
@@ -7454,16 +7616,19 @@
       <c r="AN54">
         <v>0</v>
       </c>
+      <c r="AO54">
+        <v>108</v>
+      </c>
     </row>
-    <row r="55" spans="1:40">
+    <row r="55" spans="1:41">
       <c r="A55" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B55" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C55" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D55">
         <v>12</v>
@@ -7576,16 +7741,19 @@
       <c r="AN55">
         <v>0</v>
       </c>
+      <c r="AO55">
+        <v>108</v>
+      </c>
     </row>
-    <row r="56" spans="1:40">
+    <row r="56" spans="1:41">
       <c r="A56" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B56" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C56" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D56">
         <v>12</v>
@@ -7698,16 +7866,19 @@
       <c r="AN56">
         <v>0</v>
       </c>
+      <c r="AO56">
+        <v>108</v>
+      </c>
     </row>
-    <row r="57" spans="1:40">
+    <row r="57" spans="1:41">
       <c r="A57" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B57" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C57" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D57">
         <v>12</v>
@@ -7820,16 +7991,19 @@
       <c r="AN57">
         <v>0</v>
       </c>
+      <c r="AO57">
+        <v>108</v>
+      </c>
     </row>
-    <row r="58" spans="1:40">
+    <row r="58" spans="1:41">
       <c r="A58" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B58" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C58" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D58">
         <v>12</v>
@@ -7942,992 +8116,1019 @@
       <c r="AN58">
         <v>0</v>
       </c>
+      <c r="AO58">
+        <v>144</v>
+      </c>
     </row>
-    <row r="59" spans="1:40">
+    <row r="59" spans="1:41">
       <c r="A59" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B59" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C59" t="s">
+        <v>173</v>
+      </c>
+      <c r="D59">
+        <v>12</v>
+      </c>
+      <c r="E59" t="b">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>2</v>
+      </c>
+      <c r="G59">
+        <v>12</v>
+      </c>
+      <c r="H59" t="b">
+        <v>1</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>2</v>
+      </c>
+      <c r="M59">
+        <v>12</v>
+      </c>
+      <c r="N59" t="b">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>2</v>
+      </c>
+      <c r="P59">
+        <v>12</v>
+      </c>
+      <c r="Q59" t="b">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>2</v>
+      </c>
+      <c r="S59">
+        <v>12</v>
+      </c>
+      <c r="T59" t="b">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>2</v>
+      </c>
+      <c r="V59">
+        <v>12</v>
+      </c>
+      <c r="W59" t="b">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>2</v>
+      </c>
+      <c r="Y59">
+        <v>12</v>
+      </c>
+      <c r="Z59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA59">
+        <v>2</v>
+      </c>
+      <c r="AB59">
+        <v>12</v>
+      </c>
+      <c r="AC59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD59">
+        <v>2</v>
+      </c>
+      <c r="AE59">
+        <v>12</v>
+      </c>
+      <c r="AF59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59">
+        <v>2</v>
+      </c>
+      <c r="AH59">
+        <v>12</v>
+      </c>
+      <c r="AI59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ59">
+        <v>0</v>
+      </c>
+      <c r="AK59">
+        <v>0</v>
+      </c>
+      <c r="AL59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM59">
+        <v>0</v>
+      </c>
+      <c r="AN59">
+        <v>0</v>
+      </c>
+      <c r="AO59">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="60" spans="1:41">
+      <c r="A60" t="s">
+        <v>99</v>
+      </c>
+      <c r="B60" t="s">
+        <v>165</v>
+      </c>
+      <c r="C60" t="s">
+        <v>173</v>
+      </c>
+      <c r="D60">
+        <v>12</v>
+      </c>
+      <c r="E60" t="b">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>2</v>
+      </c>
+      <c r="G60">
+        <v>12</v>
+      </c>
+      <c r="H60" t="b">
+        <v>1</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>2</v>
+      </c>
+      <c r="M60">
+        <v>12</v>
+      </c>
+      <c r="N60" t="b">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>2</v>
+      </c>
+      <c r="P60">
+        <v>12</v>
+      </c>
+      <c r="Q60" t="b">
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>2</v>
+      </c>
+      <c r="S60">
+        <v>12</v>
+      </c>
+      <c r="T60" t="b">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>2</v>
+      </c>
+      <c r="V60">
+        <v>12</v>
+      </c>
+      <c r="W60" t="b">
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>2</v>
+      </c>
+      <c r="Y60">
+        <v>12</v>
+      </c>
+      <c r="Z60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA60">
+        <v>2</v>
+      </c>
+      <c r="AB60">
+        <v>12</v>
+      </c>
+      <c r="AC60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD60">
+        <v>2</v>
+      </c>
+      <c r="AE60">
+        <v>12</v>
+      </c>
+      <c r="AF60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60">
+        <v>2</v>
+      </c>
+      <c r="AH60">
+        <v>12</v>
+      </c>
+      <c r="AI60" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ60">
+        <v>0</v>
+      </c>
+      <c r="AK60">
+        <v>0</v>
+      </c>
+      <c r="AL60" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM60">
+        <v>0</v>
+      </c>
+      <c r="AN60">
+        <v>0</v>
+      </c>
+      <c r="AO60">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="61" spans="1:41">
+      <c r="A61" t="s">
+        <v>100</v>
+      </c>
+      <c r="B61" t="s">
+        <v>166</v>
+      </c>
+      <c r="C61" t="s">
+        <v>173</v>
+      </c>
+      <c r="D61">
+        <v>12</v>
+      </c>
+      <c r="E61" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>2</v>
+      </c>
+      <c r="G61">
+        <v>12</v>
+      </c>
+      <c r="H61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>2</v>
+      </c>
+      <c r="M61">
+        <v>12</v>
+      </c>
+      <c r="N61" t="b">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>2</v>
+      </c>
+      <c r="P61">
+        <v>12</v>
+      </c>
+      <c r="Q61" t="b">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>2</v>
+      </c>
+      <c r="S61">
+        <v>12</v>
+      </c>
+      <c r="T61" t="b">
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <v>2</v>
+      </c>
+      <c r="V61">
+        <v>12</v>
+      </c>
+      <c r="W61" t="b">
+        <v>0</v>
+      </c>
+      <c r="X61">
+        <v>2</v>
+      </c>
+      <c r="Y61">
+        <v>12</v>
+      </c>
+      <c r="Z61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA61">
+        <v>2</v>
+      </c>
+      <c r="AB61">
+        <v>12</v>
+      </c>
+      <c r="AC61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD61">
+        <v>2</v>
+      </c>
+      <c r="AE61">
+        <v>12</v>
+      </c>
+      <c r="AF61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61">
+        <v>2</v>
+      </c>
+      <c r="AH61">
+        <v>12</v>
+      </c>
+      <c r="AI61" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ61">
+        <v>0</v>
+      </c>
+      <c r="AK61">
+        <v>0</v>
+      </c>
+      <c r="AL61" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM61">
+        <v>0</v>
+      </c>
+      <c r="AN61">
+        <v>0</v>
+      </c>
+      <c r="AO61">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="62" spans="1:41">
+      <c r="A62" t="s">
+        <v>101</v>
+      </c>
+      <c r="B62" t="s">
+        <v>167</v>
+      </c>
+      <c r="C62" t="s">
+        <v>173</v>
+      </c>
+      <c r="D62">
+        <v>12</v>
+      </c>
+      <c r="E62" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="G62">
+        <v>12</v>
+      </c>
+      <c r="H62" t="b">
+        <v>1</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>2</v>
+      </c>
+      <c r="M62">
+        <v>12</v>
+      </c>
+      <c r="N62" t="b">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>2</v>
+      </c>
+      <c r="P62">
+        <v>12</v>
+      </c>
+      <c r="Q62" t="b">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>2</v>
+      </c>
+      <c r="S62">
+        <v>12</v>
+      </c>
+      <c r="T62" t="b">
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <v>2</v>
+      </c>
+      <c r="V62">
+        <v>12</v>
+      </c>
+      <c r="W62" t="b">
+        <v>0</v>
+      </c>
+      <c r="X62">
+        <v>2</v>
+      </c>
+      <c r="Y62">
+        <v>12</v>
+      </c>
+      <c r="Z62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA62">
+        <v>2</v>
+      </c>
+      <c r="AB62">
+        <v>12</v>
+      </c>
+      <c r="AC62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD62">
+        <v>2</v>
+      </c>
+      <c r="AE62">
+        <v>12</v>
+      </c>
+      <c r="AF62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62">
+        <v>2</v>
+      </c>
+      <c r="AH62">
+        <v>12</v>
+      </c>
+      <c r="AI62" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ62">
+        <v>0</v>
+      </c>
+      <c r="AK62">
+        <v>0</v>
+      </c>
+      <c r="AL62" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM62">
+        <v>0</v>
+      </c>
+      <c r="AN62">
+        <v>0</v>
+      </c>
+      <c r="AO62">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="63" spans="1:41">
+      <c r="A63" t="s">
+        <v>102</v>
+      </c>
+      <c r="B63" t="s">
+        <v>168</v>
+      </c>
+      <c r="C63" t="s">
+        <v>173</v>
+      </c>
+      <c r="D63">
+        <v>12</v>
+      </c>
+      <c r="E63" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>2</v>
+      </c>
+      <c r="G63">
+        <v>12</v>
+      </c>
+      <c r="H63" t="b">
+        <v>1</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>2</v>
+      </c>
+      <c r="M63">
+        <v>12</v>
+      </c>
+      <c r="N63" t="b">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>2</v>
+      </c>
+      <c r="P63">
+        <v>12</v>
+      </c>
+      <c r="Q63" t="b">
+        <v>1</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63" t="b">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>2</v>
+      </c>
+      <c r="V63">
+        <v>12</v>
+      </c>
+      <c r="W63" t="b">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>2</v>
+      </c>
+      <c r="Y63">
+        <v>12</v>
+      </c>
+      <c r="Z63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA63">
+        <v>2</v>
+      </c>
+      <c r="AB63">
+        <v>12</v>
+      </c>
+      <c r="AC63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD63">
+        <v>2</v>
+      </c>
+      <c r="AE63">
+        <v>12</v>
+      </c>
+      <c r="AF63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63">
+        <v>2</v>
+      </c>
+      <c r="AH63">
+        <v>12</v>
+      </c>
+      <c r="AI63" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ63">
+        <v>0</v>
+      </c>
+      <c r="AK63">
+        <v>0</v>
+      </c>
+      <c r="AL63" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM63">
+        <v>0</v>
+      </c>
+      <c r="AN63">
+        <v>0</v>
+      </c>
+      <c r="AO63">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="64" spans="1:41">
+      <c r="A64" t="s">
+        <v>103</v>
+      </c>
+      <c r="B64" t="s">
+        <v>169</v>
+      </c>
+      <c r="C64" t="s">
+        <v>173</v>
+      </c>
+      <c r="D64">
+        <v>12</v>
+      </c>
+      <c r="E64" t="b">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>2</v>
+      </c>
+      <c r="G64">
+        <v>12</v>
+      </c>
+      <c r="H64" t="b">
+        <v>1</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>2</v>
+      </c>
+      <c r="M64">
+        <v>12</v>
+      </c>
+      <c r="N64" t="b">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>2</v>
+      </c>
+      <c r="P64">
+        <v>12</v>
+      </c>
+      <c r="Q64" t="b">
+        <v>1</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64" t="b">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>2</v>
+      </c>
+      <c r="V64">
+        <v>12</v>
+      </c>
+      <c r="W64" t="b">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>2</v>
+      </c>
+      <c r="Y64">
+        <v>12</v>
+      </c>
+      <c r="Z64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA64">
+        <v>2</v>
+      </c>
+      <c r="AB64">
+        <v>12</v>
+      </c>
+      <c r="AC64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD64">
+        <v>2</v>
+      </c>
+      <c r="AE64">
+        <v>12</v>
+      </c>
+      <c r="AF64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64">
+        <v>2</v>
+      </c>
+      <c r="AH64">
+        <v>12</v>
+      </c>
+      <c r="AI64" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ64">
+        <v>0</v>
+      </c>
+      <c r="AK64">
+        <v>0</v>
+      </c>
+      <c r="AL64" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM64">
+        <v>0</v>
+      </c>
+      <c r="AN64">
+        <v>0</v>
+      </c>
+      <c r="AO64">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="65" spans="1:41">
+      <c r="A65" t="s">
+        <v>104</v>
+      </c>
+      <c r="B65" t="s">
+        <v>170</v>
+      </c>
+      <c r="C65" t="s">
+        <v>173</v>
+      </c>
+      <c r="D65">
+        <v>12</v>
+      </c>
+      <c r="E65" t="b">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>2</v>
+      </c>
+      <c r="G65">
+        <v>12</v>
+      </c>
+      <c r="H65" t="b">
+        <v>1</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>2</v>
+      </c>
+      <c r="M65">
+        <v>12</v>
+      </c>
+      <c r="N65" t="b">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>2</v>
+      </c>
+      <c r="P65">
+        <v>12</v>
+      </c>
+      <c r="Q65" t="b">
+        <v>1</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65" t="b">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>2</v>
+      </c>
+      <c r="V65">
+        <v>12</v>
+      </c>
+      <c r="W65" t="b">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>2</v>
+      </c>
+      <c r="Y65">
+        <v>12</v>
+      </c>
+      <c r="Z65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>2</v>
+      </c>
+      <c r="AB65">
+        <v>12</v>
+      </c>
+      <c r="AC65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD65">
+        <v>2</v>
+      </c>
+      <c r="AE65">
+        <v>12</v>
+      </c>
+      <c r="AF65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65">
+        <v>2</v>
+      </c>
+      <c r="AH65">
+        <v>12</v>
+      </c>
+      <c r="AI65" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ65">
+        <v>0</v>
+      </c>
+      <c r="AK65">
+        <v>0</v>
+      </c>
+      <c r="AL65" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM65">
+        <v>0</v>
+      </c>
+      <c r="AN65">
+        <v>0</v>
+      </c>
+      <c r="AO65">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="66" spans="1:41">
+      <c r="A66" t="s">
+        <v>105</v>
+      </c>
+      <c r="B66" t="s">
+        <v>171</v>
+      </c>
+      <c r="C66" t="s">
+        <v>173</v>
+      </c>
+      <c r="D66">
+        <v>12</v>
+      </c>
+      <c r="E66" t="b">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>2</v>
+      </c>
+      <c r="G66">
+        <v>12</v>
+      </c>
+      <c r="H66" t="b">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>2</v>
+      </c>
+      <c r="M66">
+        <v>12</v>
+      </c>
+      <c r="N66" t="b">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>2</v>
+      </c>
+      <c r="P66">
+        <v>12</v>
+      </c>
+      <c r="Q66" t="b">
+        <v>1</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66" t="b">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>2</v>
+      </c>
+      <c r="V66">
+        <v>12</v>
+      </c>
+      <c r="W66" t="b">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>2</v>
+      </c>
+      <c r="Y66">
+        <v>12</v>
+      </c>
+      <c r="Z66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA66">
+        <v>2</v>
+      </c>
+      <c r="AB66">
+        <v>12</v>
+      </c>
+      <c r="AC66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD66">
+        <v>2</v>
+      </c>
+      <c r="AE66">
+        <v>12</v>
+      </c>
+      <c r="AF66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66">
+        <v>2</v>
+      </c>
+      <c r="AH66">
+        <v>12</v>
+      </c>
+      <c r="AI66" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ66">
+        <v>0</v>
+      </c>
+      <c r="AK66">
+        <v>0</v>
+      </c>
+      <c r="AL66" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM66">
+        <v>0</v>
+      </c>
+      <c r="AN66">
+        <v>0</v>
+      </c>
+      <c r="AO66">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="67" spans="1:41">
+      <c r="A67" t="s">
+        <v>106</v>
+      </c>
+      <c r="B67" t="s">
         <v>172</v>
       </c>
-      <c r="D59">
-        <v>12</v>
-      </c>
-      <c r="E59" t="b">
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <v>2</v>
-      </c>
-      <c r="G59">
-        <v>12</v>
-      </c>
-      <c r="H59" t="b">
-        <v>1</v>
-      </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59" t="b">
-        <v>0</v>
-      </c>
-      <c r="L59">
-        <v>2</v>
-      </c>
-      <c r="M59">
-        <v>12</v>
-      </c>
-      <c r="N59" t="b">
-        <v>0</v>
-      </c>
-      <c r="O59">
-        <v>2</v>
-      </c>
-      <c r="P59">
-        <v>12</v>
-      </c>
-      <c r="Q59" t="b">
-        <v>0</v>
-      </c>
-      <c r="R59">
-        <v>2</v>
-      </c>
-      <c r="S59">
-        <v>12</v>
-      </c>
-      <c r="T59" t="b">
-        <v>0</v>
-      </c>
-      <c r="U59">
-        <v>2</v>
-      </c>
-      <c r="V59">
-        <v>12</v>
-      </c>
-      <c r="W59" t="b">
-        <v>0</v>
-      </c>
-      <c r="X59">
-        <v>2</v>
-      </c>
-      <c r="Y59">
-        <v>12</v>
-      </c>
-      <c r="Z59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA59">
-        <v>2</v>
-      </c>
-      <c r="AB59">
-        <v>12</v>
-      </c>
-      <c r="AC59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD59">
-        <v>2</v>
-      </c>
-      <c r="AE59">
-        <v>12</v>
-      </c>
-      <c r="AF59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59">
-        <v>2</v>
-      </c>
-      <c r="AH59">
-        <v>12</v>
-      </c>
-      <c r="AI59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ59">
-        <v>0</v>
-      </c>
-      <c r="AK59">
-        <v>0</v>
-      </c>
-      <c r="AL59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM59">
-        <v>0</v>
-      </c>
-      <c r="AN59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:40">
-      <c r="A60" t="s">
-        <v>98</v>
-      </c>
-      <c r="B60" t="s">
-        <v>164</v>
-      </c>
-      <c r="C60" t="s">
-        <v>172</v>
-      </c>
-      <c r="D60">
-        <v>12</v>
-      </c>
-      <c r="E60" t="b">
-        <v>0</v>
-      </c>
-      <c r="F60">
-        <v>2</v>
-      </c>
-      <c r="G60">
-        <v>12</v>
-      </c>
-      <c r="H60" t="b">
-        <v>1</v>
-      </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60">
-        <v>0</v>
-      </c>
-      <c r="K60" t="b">
-        <v>0</v>
-      </c>
-      <c r="L60">
-        <v>2</v>
-      </c>
-      <c r="M60">
-        <v>12</v>
-      </c>
-      <c r="N60" t="b">
-        <v>0</v>
-      </c>
-      <c r="O60">
-        <v>2</v>
-      </c>
-      <c r="P60">
-        <v>12</v>
-      </c>
-      <c r="Q60" t="b">
-        <v>0</v>
-      </c>
-      <c r="R60">
-        <v>2</v>
-      </c>
-      <c r="S60">
-        <v>12</v>
-      </c>
-      <c r="T60" t="b">
-        <v>0</v>
-      </c>
-      <c r="U60">
-        <v>2</v>
-      </c>
-      <c r="V60">
-        <v>12</v>
-      </c>
-      <c r="W60" t="b">
-        <v>0</v>
-      </c>
-      <c r="X60">
-        <v>2</v>
-      </c>
-      <c r="Y60">
-        <v>12</v>
-      </c>
-      <c r="Z60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA60">
-        <v>2</v>
-      </c>
-      <c r="AB60">
-        <v>12</v>
-      </c>
-      <c r="AC60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD60">
-        <v>2</v>
-      </c>
-      <c r="AE60">
-        <v>12</v>
-      </c>
-      <c r="AF60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60">
-        <v>2</v>
-      </c>
-      <c r="AH60">
-        <v>12</v>
-      </c>
-      <c r="AI60" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ60">
-        <v>0</v>
-      </c>
-      <c r="AK60">
-        <v>0</v>
-      </c>
-      <c r="AL60" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM60">
-        <v>0</v>
-      </c>
-      <c r="AN60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:40">
-      <c r="A61" t="s">
-        <v>99</v>
-      </c>
-      <c r="B61" t="s">
-        <v>165</v>
-      </c>
-      <c r="C61" t="s">
-        <v>172</v>
-      </c>
-      <c r="D61">
-        <v>12</v>
-      </c>
-      <c r="E61" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61">
-        <v>2</v>
-      </c>
-      <c r="G61">
-        <v>12</v>
-      </c>
-      <c r="H61" t="b">
-        <v>1</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61" t="b">
-        <v>0</v>
-      </c>
-      <c r="L61">
-        <v>2</v>
-      </c>
-      <c r="M61">
-        <v>12</v>
-      </c>
-      <c r="N61" t="b">
-        <v>0</v>
-      </c>
-      <c r="O61">
-        <v>2</v>
-      </c>
-      <c r="P61">
-        <v>12</v>
-      </c>
-      <c r="Q61" t="b">
-        <v>0</v>
-      </c>
-      <c r="R61">
-        <v>2</v>
-      </c>
-      <c r="S61">
-        <v>12</v>
-      </c>
-      <c r="T61" t="b">
-        <v>0</v>
-      </c>
-      <c r="U61">
-        <v>2</v>
-      </c>
-      <c r="V61">
-        <v>12</v>
-      </c>
-      <c r="W61" t="b">
-        <v>0</v>
-      </c>
-      <c r="X61">
-        <v>2</v>
-      </c>
-      <c r="Y61">
-        <v>12</v>
-      </c>
-      <c r="Z61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA61">
-        <v>2</v>
-      </c>
-      <c r="AB61">
-        <v>12</v>
-      </c>
-      <c r="AC61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD61">
-        <v>2</v>
-      </c>
-      <c r="AE61">
-        <v>12</v>
-      </c>
-      <c r="AF61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG61">
-        <v>2</v>
-      </c>
-      <c r="AH61">
-        <v>12</v>
-      </c>
-      <c r="AI61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ61">
-        <v>0</v>
-      </c>
-      <c r="AK61">
-        <v>0</v>
-      </c>
-      <c r="AL61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM61">
-        <v>0</v>
-      </c>
-      <c r="AN61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:40">
-      <c r="A62" t="s">
-        <v>100</v>
-      </c>
-      <c r="B62" t="s">
-        <v>166</v>
-      </c>
-      <c r="C62" t="s">
-        <v>172</v>
-      </c>
-      <c r="D62">
-        <v>12</v>
-      </c>
-      <c r="E62" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62">
-        <v>2</v>
-      </c>
-      <c r="G62">
-        <v>12</v>
-      </c>
-      <c r="H62" t="b">
-        <v>1</v>
-      </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62" t="b">
-        <v>0</v>
-      </c>
-      <c r="L62">
-        <v>2</v>
-      </c>
-      <c r="M62">
-        <v>12</v>
-      </c>
-      <c r="N62" t="b">
-        <v>0</v>
-      </c>
-      <c r="O62">
-        <v>2</v>
-      </c>
-      <c r="P62">
-        <v>12</v>
-      </c>
-      <c r="Q62" t="b">
-        <v>0</v>
-      </c>
-      <c r="R62">
-        <v>2</v>
-      </c>
-      <c r="S62">
-        <v>12</v>
-      </c>
-      <c r="T62" t="b">
-        <v>0</v>
-      </c>
-      <c r="U62">
-        <v>2</v>
-      </c>
-      <c r="V62">
-        <v>12</v>
-      </c>
-      <c r="W62" t="b">
-        <v>0</v>
-      </c>
-      <c r="X62">
-        <v>2</v>
-      </c>
-      <c r="Y62">
-        <v>12</v>
-      </c>
-      <c r="Z62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA62">
-        <v>2</v>
-      </c>
-      <c r="AB62">
-        <v>12</v>
-      </c>
-      <c r="AC62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD62">
-        <v>2</v>
-      </c>
-      <c r="AE62">
-        <v>12</v>
-      </c>
-      <c r="AF62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG62">
-        <v>2</v>
-      </c>
-      <c r="AH62">
-        <v>12</v>
-      </c>
-      <c r="AI62" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ62">
-        <v>0</v>
-      </c>
-      <c r="AK62">
-        <v>0</v>
-      </c>
-      <c r="AL62" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM62">
-        <v>0</v>
-      </c>
-      <c r="AN62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:40">
-      <c r="A63" t="s">
-        <v>101</v>
-      </c>
-      <c r="B63" t="s">
-        <v>167</v>
-      </c>
-      <c r="C63" t="s">
-        <v>172</v>
-      </c>
-      <c r="D63">
-        <v>12</v>
-      </c>
-      <c r="E63" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63">
-        <v>2</v>
-      </c>
-      <c r="G63">
-        <v>12</v>
-      </c>
-      <c r="H63" t="b">
-        <v>1</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63" t="b">
-        <v>0</v>
-      </c>
-      <c r="L63">
-        <v>2</v>
-      </c>
-      <c r="M63">
-        <v>12</v>
-      </c>
-      <c r="N63" t="b">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>2</v>
-      </c>
-      <c r="P63">
-        <v>12</v>
-      </c>
-      <c r="Q63" t="b">
-        <v>1</v>
-      </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63">
-        <v>0</v>
-      </c>
-      <c r="T63" t="b">
-        <v>0</v>
-      </c>
-      <c r="U63">
-        <v>2</v>
-      </c>
-      <c r="V63">
-        <v>12</v>
-      </c>
-      <c r="W63" t="b">
-        <v>0</v>
-      </c>
-      <c r="X63">
-        <v>2</v>
-      </c>
-      <c r="Y63">
-        <v>12</v>
-      </c>
-      <c r="Z63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA63">
-        <v>2</v>
-      </c>
-      <c r="AB63">
-        <v>12</v>
-      </c>
-      <c r="AC63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD63">
-        <v>2</v>
-      </c>
-      <c r="AE63">
-        <v>12</v>
-      </c>
-      <c r="AF63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63">
-        <v>2</v>
-      </c>
-      <c r="AH63">
-        <v>12</v>
-      </c>
-      <c r="AI63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ63">
-        <v>0</v>
-      </c>
-      <c r="AK63">
-        <v>0</v>
-      </c>
-      <c r="AL63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM63">
-        <v>0</v>
-      </c>
-      <c r="AN63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:40">
-      <c r="A64" t="s">
-        <v>102</v>
-      </c>
-      <c r="B64" t="s">
-        <v>168</v>
-      </c>
-      <c r="C64" t="s">
-        <v>172</v>
-      </c>
-      <c r="D64">
-        <v>12</v>
-      </c>
-      <c r="E64" t="b">
-        <v>0</v>
-      </c>
-      <c r="F64">
-        <v>2</v>
-      </c>
-      <c r="G64">
-        <v>12</v>
-      </c>
-      <c r="H64" t="b">
-        <v>1</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64" t="b">
-        <v>0</v>
-      </c>
-      <c r="L64">
-        <v>2</v>
-      </c>
-      <c r="M64">
-        <v>12</v>
-      </c>
-      <c r="N64" t="b">
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <v>2</v>
-      </c>
-      <c r="P64">
-        <v>12</v>
-      </c>
-      <c r="Q64" t="b">
-        <v>1</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="S64">
-        <v>0</v>
-      </c>
-      <c r="T64" t="b">
-        <v>0</v>
-      </c>
-      <c r="U64">
-        <v>2</v>
-      </c>
-      <c r="V64">
-        <v>12</v>
-      </c>
-      <c r="W64" t="b">
-        <v>0</v>
-      </c>
-      <c r="X64">
-        <v>2</v>
-      </c>
-      <c r="Y64">
-        <v>12</v>
-      </c>
-      <c r="Z64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA64">
-        <v>2</v>
-      </c>
-      <c r="AB64">
-        <v>12</v>
-      </c>
-      <c r="AC64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD64">
-        <v>2</v>
-      </c>
-      <c r="AE64">
-        <v>12</v>
-      </c>
-      <c r="AF64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64">
-        <v>2</v>
-      </c>
-      <c r="AH64">
-        <v>12</v>
-      </c>
-      <c r="AI64" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ64">
-        <v>0</v>
-      </c>
-      <c r="AK64">
-        <v>0</v>
-      </c>
-      <c r="AL64" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM64">
-        <v>0</v>
-      </c>
-      <c r="AN64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:40">
-      <c r="A65" t="s">
-        <v>103</v>
-      </c>
-      <c r="B65" t="s">
-        <v>169</v>
-      </c>
-      <c r="C65" t="s">
-        <v>172</v>
-      </c>
-      <c r="D65">
-        <v>12</v>
-      </c>
-      <c r="E65" t="b">
-        <v>0</v>
-      </c>
-      <c r="F65">
-        <v>2</v>
-      </c>
-      <c r="G65">
-        <v>12</v>
-      </c>
-      <c r="H65" t="b">
-        <v>1</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65" t="b">
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <v>2</v>
-      </c>
-      <c r="M65">
-        <v>12</v>
-      </c>
-      <c r="N65" t="b">
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <v>2</v>
-      </c>
-      <c r="P65">
-        <v>12</v>
-      </c>
-      <c r="Q65" t="b">
-        <v>1</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>0</v>
-      </c>
-      <c r="T65" t="b">
-        <v>0</v>
-      </c>
-      <c r="U65">
-        <v>2</v>
-      </c>
-      <c r="V65">
-        <v>12</v>
-      </c>
-      <c r="W65" t="b">
-        <v>0</v>
-      </c>
-      <c r="X65">
-        <v>2</v>
-      </c>
-      <c r="Y65">
-        <v>12</v>
-      </c>
-      <c r="Z65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA65">
-        <v>2</v>
-      </c>
-      <c r="AB65">
-        <v>12</v>
-      </c>
-      <c r="AC65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD65">
-        <v>2</v>
-      </c>
-      <c r="AE65">
-        <v>12</v>
-      </c>
-      <c r="AF65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65">
-        <v>2</v>
-      </c>
-      <c r="AH65">
-        <v>12</v>
-      </c>
-      <c r="AI65" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ65">
-        <v>0</v>
-      </c>
-      <c r="AK65">
-        <v>0</v>
-      </c>
-      <c r="AL65" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM65">
-        <v>0</v>
-      </c>
-      <c r="AN65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:40">
-      <c r="A66" t="s">
-        <v>104</v>
-      </c>
-      <c r="B66" t="s">
-        <v>170</v>
-      </c>
-      <c r="C66" t="s">
-        <v>172</v>
-      </c>
-      <c r="D66">
-        <v>12</v>
-      </c>
-      <c r="E66" t="b">
-        <v>0</v>
-      </c>
-      <c r="F66">
-        <v>2</v>
-      </c>
-      <c r="G66">
-        <v>12</v>
-      </c>
-      <c r="H66" t="b">
-        <v>1</v>
-      </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66" t="b">
-        <v>0</v>
-      </c>
-      <c r="L66">
-        <v>2</v>
-      </c>
-      <c r="M66">
-        <v>12</v>
-      </c>
-      <c r="N66" t="b">
-        <v>0</v>
-      </c>
-      <c r="O66">
-        <v>2</v>
-      </c>
-      <c r="P66">
-        <v>12</v>
-      </c>
-      <c r="Q66" t="b">
-        <v>1</v>
-      </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="S66">
-        <v>0</v>
-      </c>
-      <c r="T66" t="b">
-        <v>0</v>
-      </c>
-      <c r="U66">
-        <v>2</v>
-      </c>
-      <c r="V66">
-        <v>12</v>
-      </c>
-      <c r="W66" t="b">
-        <v>0</v>
-      </c>
-      <c r="X66">
-        <v>2</v>
-      </c>
-      <c r="Y66">
-        <v>12</v>
-      </c>
-      <c r="Z66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA66">
-        <v>2</v>
-      </c>
-      <c r="AB66">
-        <v>12</v>
-      </c>
-      <c r="AC66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD66">
-        <v>2</v>
-      </c>
-      <c r="AE66">
-        <v>12</v>
-      </c>
-      <c r="AF66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG66">
-        <v>2</v>
-      </c>
-      <c r="AH66">
-        <v>12</v>
-      </c>
-      <c r="AI66" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ66">
-        <v>0</v>
-      </c>
-      <c r="AK66">
-        <v>0</v>
-      </c>
-      <c r="AL66" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM66">
-        <v>0</v>
-      </c>
-      <c r="AN66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:40">
-      <c r="A67" t="s">
-        <v>105</v>
-      </c>
-      <c r="B67" t="s">
-        <v>171</v>
-      </c>
       <c r="C67" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D67">
         <v>12</v>
@@ -9039,6 +9240,9 @@
       </c>
       <c r="AN67">
         <v>0</v>
+      </c>
+      <c r="AO67">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Rules/Evangers Rules Matrix.xlsx
+++ b/Data/Rules/Evangers Rules Matrix.xlsx
@@ -1182,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="V3">
         <v>24</v>
@@ -6093,10 +6093,10 @@
         <v>0</v>
       </c>
       <c r="AG42">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AH42">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AI42" t="b">
         <v>1</v>
@@ -6117,7 +6117,7 @@
         <v>0</v>
       </c>
       <c r="AO42">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:41">
